--- a/スペースギャラクシー仕様書_完成版.xlsx
+++ b/スペースギャラクシー仕様書_完成版.xlsx
@@ -5,27 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA3\Desktop\3156\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA3\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="1" r:id="rId1"/>
     <sheet name="ルール" sheetId="2" r:id="rId2"/>
     <sheet name="フロー" sheetId="3" r:id="rId3"/>
-    <sheet name="戦略・やりがい" sheetId="4" r:id="rId4"/>
-    <sheet name="UI設計" sheetId="5" r:id="rId5"/>
-    <sheet name="画面遷移" sheetId="6" r:id="rId6"/>
-    <sheet name="タスク" sheetId="7" r:id="rId7"/>
+    <sheet name="ゲーム画面" sheetId="5" r:id="rId4"/>
+    <sheet name="画面遷移" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>項目</t>
   </si>
@@ -87,173 +85,61 @@
     <t>酸素</t>
   </si>
   <si>
+    <t>終了条件</t>
+  </si>
+  <si>
+    <t>酸素が0で終了</t>
+  </si>
+  <si>
+    <t>得点</t>
+  </si>
+  <si>
+    <t>コア数 + 残り酸素</t>
+  </si>
+  <si>
+    <t>勝敗</t>
+  </si>
+  <si>
+    <t>遷移元</t>
+  </si>
+  <si>
+    <t>遷移先</t>
+  </si>
+  <si>
+    <t>タイトル</t>
+  </si>
+  <si>
+    <t>ゲーム画面</t>
+  </si>
+  <si>
+    <t>ゲーム</t>
+  </si>
+  <si>
+    <t>リザルト</t>
+  </si>
+  <si>
+    <t>次ラウンド or タイトル</t>
+  </si>
+  <si>
+    <t>3ラウンドの得点の合計</t>
+    <rPh sb="6" eb="8">
+      <t>トクテン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ゴウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>毎ターン 基本1 + コア数 減少</t>
-  </si>
-  <si>
-    <t>終了条件</t>
-  </si>
-  <si>
-    <t>酸素が0で終了</t>
-  </si>
-  <si>
-    <t>得点</t>
-  </si>
-  <si>
-    <t>コア数 + 残り酸素</t>
-  </si>
-  <si>
-    <t>勝敗</t>
-  </si>
-  <si>
-    <t>3ラウンド合計</t>
-  </si>
-  <si>
-    <t>種類</t>
-  </si>
-  <si>
-    <t>手順</t>
-  </si>
-  <si>
-    <t>ターン</t>
-  </si>
-  <si>
-    <t>サイコロ→移動→マス効果→酸素減少→交代</t>
-  </si>
-  <si>
-    <t>ラウンド</t>
-  </si>
-  <si>
-    <t>開始→収集→酸素尽きる→得点</t>
-  </si>
-  <si>
-    <t>全体</t>
-  </si>
-  <si>
-    <t>3ラウンド→合計スコア</t>
-  </si>
-  <si>
-    <t>戦略</t>
-  </si>
-  <si>
-    <t>早帰り or 欲張り</t>
-  </si>
-  <si>
-    <t>ジレンマ</t>
-  </si>
-  <si>
-    <t>コア増加で不利になる</t>
-  </si>
-  <si>
-    <t>対人要素</t>
-  </si>
-  <si>
-    <t>酸素共有による心理戦</t>
-  </si>
-  <si>
-    <t>やりがい</t>
-  </si>
-  <si>
-    <t>判断の連続と達成感</t>
-  </si>
-  <si>
-    <t>リプレイ性</t>
-  </si>
-  <si>
-    <t>プレイスタイルで展開変化</t>
-  </si>
-  <si>
-    <t>画面</t>
-  </si>
-  <si>
-    <t>要素</t>
-  </si>
-  <si>
-    <t>メイン</t>
-  </si>
-  <si>
-    <t>マップ・プレイヤー・酸素ゲージ</t>
-  </si>
-  <si>
-    <t>情報UI</t>
-  </si>
-  <si>
-    <t>コア数・ターン表示</t>
-  </si>
-  <si>
-    <t>操作</t>
-  </si>
-  <si>
-    <t>サイコロボタン</t>
-  </si>
-  <si>
-    <t>結果</t>
-  </si>
-  <si>
-    <t>スコア表示</t>
-  </si>
-  <si>
-    <t>遷移元</t>
-  </si>
-  <si>
-    <t>遷移先</t>
-  </si>
-  <si>
-    <t>タイトル</t>
-  </si>
-  <si>
-    <t>ゲーム画面</t>
-  </si>
-  <si>
-    <t>ゲーム</t>
-  </si>
-  <si>
-    <t>リザルト</t>
-  </si>
-  <si>
-    <t>次ラウンド or タイトル</t>
-  </si>
-  <si>
-    <t>タスク</t>
-  </si>
-  <si>
-    <t>システム</t>
-  </si>
-  <si>
-    <t>サイコロ処理</t>
-  </si>
-  <si>
-    <t>移動処理</t>
-  </si>
-  <si>
-    <t>酸素管理</t>
-  </si>
-  <si>
-    <t>スコア計算</t>
-  </si>
-  <si>
-    <t>UI</t>
-  </si>
-  <si>
-    <t>画面作成</t>
-  </si>
-  <si>
-    <t>表示更新</t>
-  </si>
-  <si>
-    <t>AI</t>
-  </si>
-  <si>
-    <t>CPU行動</t>
-  </si>
-  <si>
-    <t>ラウンド管理</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,6 +154,36 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -277,7 +193,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -285,12 +201,184 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -306,6 +394,1010 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="テキスト ボックス 1"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="457200" y="1076325"/>
+          <a:ext cx="1514475" cy="495300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>サイコロ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="右矢印 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2466975" y="1152525"/>
+          <a:ext cx="704850" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>188819</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>11767</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>484094</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>160805</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="テキスト ボックス 3"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9075084" y="1020296"/>
+          <a:ext cx="978834" cy="485215"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>移動</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>262218</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>124385</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>281268</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>76760</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="右矢印 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10515600" y="1132914"/>
+          <a:ext cx="702609" cy="288552"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="テキスト ボックス 5"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5972175" y="971550"/>
+          <a:ext cx="3067050" cy="495300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>お宝の取得するか</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>362510</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>101973</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>381560</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>54348</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="右矢印 6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14717245" y="1110502"/>
+          <a:ext cx="702609" cy="288552"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="テキスト ボックス 7"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15491732" y="998764"/>
+          <a:ext cx="2164897" cy="511629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>次プレイヤー</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>347382</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="テキスト ボックス 8"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2819960" y="1037104"/>
+          <a:ext cx="1628775" cy="485215"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>酸素減少</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>142876</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>156882</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="テキスト ボックス 9"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="142876" y="1046629"/>
+          <a:ext cx="1381124" cy="485215"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>スタート</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="右矢印 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1866900" y="1181100"/>
+          <a:ext cx="704850" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="右矢印 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4972050" y="1238250"/>
+          <a:ext cx="704850" cy="295275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>490260</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>147918</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>392206</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>128868</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="テキスト ボックス 13"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14777760" y="2447525"/>
+          <a:ext cx="3303732" cy="511629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>前に進む</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800"/>
+            <a:t>or</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>引き返す</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>94412</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>49585</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>382964</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>79841</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="右矢印 15"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="16198345" y="1866259"/>
+          <a:ext cx="737827" cy="288552"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>89647</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>100853</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>156882</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>156882</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="屈折矢印 17"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3491433" y="1869782"/>
+          <a:ext cx="10952949" cy="940493"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentUpArrow">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 18023"/>
+            <a:gd name="adj2" fmla="val 25000"/>
+            <a:gd name="adj3" fmla="val 25000"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>416138</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>89967</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>435188</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>42342</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="右矢印 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18105424" y="1151324"/>
+          <a:ext cx="699407" cy="306161"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>172811</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>103414</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>13607</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>84364</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="テキスト ボックス 19"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19222811" y="2049235"/>
+          <a:ext cx="3242582" cy="511629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>スタート地点に戻る</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>307731</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>65942</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>345831</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>27116</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2373923" y="234461"/>
+          <a:ext cx="8991600" cy="4848232"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -593,69 +1685,93 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="2" width="36.125" customWidth="1"/>
+    <col min="3" max="3" width="26.875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="21.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" ht="14.25" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
+    <row r="7" spans="1:5" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -663,61 +1779,66 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="12.375" customWidth="1"/>
+    <col min="2" max="2" width="29.375" customWidth="1"/>
+    <col min="3" max="3" width="20.25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="14.25" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
-        <v>20</v>
+      <c r="B4" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -728,275 +1849,63 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-    </row>
+    <row r="3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/スペースギャラクシー仕様書_完成版.xlsx
+++ b/スペースギャラクシー仕様書_完成版.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA3\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA3\Desktop\3156\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>項目</t>
   </si>
@@ -98,27 +98,6 @@
   </si>
   <si>
     <t>勝敗</t>
-  </si>
-  <si>
-    <t>遷移元</t>
-  </si>
-  <si>
-    <t>遷移先</t>
-  </si>
-  <si>
-    <t>タイトル</t>
-  </si>
-  <si>
-    <t>ゲーム画面</t>
-  </si>
-  <si>
-    <t>ゲーム</t>
-  </si>
-  <si>
-    <t>リザルト</t>
-  </si>
-  <si>
-    <t>次ラウンド or タイトル</t>
   </si>
   <si>
     <t>3ラウンドの得点の合計</t>
@@ -134,12 +113,27 @@
     <t>毎ターン 基本1 + コア数 減少</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>ゲーム画面</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フロー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーン遷移</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,6 +178,33 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="48"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="72"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -193,7 +214,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -360,11 +381,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -379,6 +437,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -907,7 +989,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:srgbClr val="FFFF00"/>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
@@ -1317,7 +1399,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:srgbClr val="FFFF00"/>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
@@ -1362,15 +1444,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>307731</xdr:colOff>
+      <xdr:colOff>58615</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>65942</xdr:rowOff>
+      <xdr:rowOff>58615</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>345831</xdr:colOff>
+      <xdr:colOff>96715</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>27116</xdr:rowOff>
+      <xdr:rowOff>5136</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1387,7 +1469,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2373923" y="234461"/>
+          <a:off x="2124807" y="468923"/>
           <a:ext cx="8991600" cy="4848232"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1395,6 +1477,429 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>149678</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="テキスト ボックス 1"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="219075" y="1009650"/>
+          <a:ext cx="1343025" cy="511628"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>タイトル</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>479371</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>16328</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="テキスト ボックス 2"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5715000" y="1047750"/>
+          <a:ext cx="1622371" cy="511628"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="92D050"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>めにゅー</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>168728</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="テキスト ボックス 3"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2743200" y="1028700"/>
+          <a:ext cx="1962150" cy="511628"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>ゲーム画面</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>149678</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="テキスト ボックス 4"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3019425" y="2724150"/>
+          <a:ext cx="1495425" cy="511628"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="00B0F0"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>リザルト</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>61232</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>91168</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="右矢印 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4848225" y="1162050"/>
+          <a:ext cx="699407" cy="300718"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>432707</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>72118</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="右矢印 6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1790700" y="1143000"/>
+          <a:ext cx="699407" cy="300718"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>208870</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114982</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>509588</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>128589</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="右矢印 7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="3438525" y="2028827"/>
+          <a:ext cx="699407" cy="300718"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1814,7 +2319,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.15">
@@ -1838,7 +2343,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1849,11 +2354,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="2" width="28.875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1" spans="1:2" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.8">
+      <c r="A1" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="15"/>
+    </row>
+    <row r="2" spans="1:2" ht="14.25" thickTop="1" x14ac:dyDescent="0.15"/>
+    <row r="3" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -1862,54 +2380,50 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="33" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="18"/>
+    </row>
+    <row r="2" spans="1:3" ht="14.25" thickTop="1" x14ac:dyDescent="0.15"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="3" max="3" width="21.75" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" t="s">
-        <v>26</v>
-      </c>
+    <row r="1" spans="1:3" ht="56.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="21"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-    </row>
+    <row r="2" spans="1:3" ht="14.25" thickTop="1" x14ac:dyDescent="0.15"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>